--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4180,6 +4180,32 @@
         <v>1.96</v>
       </c>
     </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B147">
+        <v>6.33</v>
+      </c>
+      <c r="C147">
+        <v>3.63</v>
+      </c>
+      <c r="D147">
+        <v>5.4</v>
+      </c>
+      <c r="E147">
+        <v>1.34</v>
+      </c>
+      <c r="F147">
+        <v>2.97</v>
+      </c>
+      <c r="G147">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H147">
+        <v>1.71</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4206,6 +4206,84 @@
         <v>1.71</v>
       </c>
     </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B148">
+        <v>5.76</v>
+      </c>
+      <c r="C148">
+        <v>2.4</v>
+      </c>
+      <c r="D148">
+        <v>4.09</v>
+      </c>
+      <c r="E148">
+        <v>1.41</v>
+      </c>
+      <c r="F148">
+        <v>2.38</v>
+      </c>
+      <c r="G148">
+        <v>0.74</v>
+      </c>
+      <c r="H148">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B149">
+        <v>6.57</v>
+      </c>
+      <c r="C149">
+        <v>4.59</v>
+      </c>
+      <c r="D149">
+        <v>4.62</v>
+      </c>
+      <c r="E149">
+        <v>1.2</v>
+      </c>
+      <c r="F149">
+        <v>2.13</v>
+      </c>
+      <c r="G149">
+        <v>1.37</v>
+      </c>
+      <c r="H149">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B150">
+        <v>6.43</v>
+      </c>
+      <c r="C150">
+        <v>2.5</v>
+      </c>
+      <c r="D150">
+        <v>5.31</v>
+      </c>
+      <c r="E150">
+        <v>0.99</v>
+      </c>
+      <c r="F150">
+        <v>2.19</v>
+      </c>
+      <c r="G150">
+        <v>1.44</v>
+      </c>
+      <c r="H150">
+        <v>1.72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4284,6 +4284,32 @@
         <v>1.72</v>
       </c>
     </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B151">
+        <v>6.11</v>
+      </c>
+      <c r="C151">
+        <v>3.14</v>
+      </c>
+      <c r="D151">
+        <v>5.09</v>
+      </c>
+      <c r="E151">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F151">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G151">
+        <v>0.78</v>
+      </c>
+      <c r="H151">
+        <v>1.84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4310,6 +4310,32 @@
         <v>1.84</v>
       </c>
     </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B152">
+        <v>6.35</v>
+      </c>
+      <c r="C152">
+        <v>2.83</v>
+      </c>
+      <c r="D152">
+        <v>5.03</v>
+      </c>
+      <c r="E152">
+        <v>1.44</v>
+      </c>
+      <c r="F152">
+        <v>2.21</v>
+      </c>
+      <c r="G152">
+        <v>0.88</v>
+      </c>
+      <c r="H152">
+        <v>1.56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4336,6 +4336,32 @@
         <v>1.56</v>
       </c>
     </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B153">
+        <v>5.98</v>
+      </c>
+      <c r="C153">
+        <v>3.13</v>
+      </c>
+      <c r="D153">
+        <v>4.5</v>
+      </c>
+      <c r="E153">
+        <v>0.92</v>
+      </c>
+      <c r="F153">
+        <v>2.61</v>
+      </c>
+      <c r="G153">
+        <v>0.8</v>
+      </c>
+      <c r="H153">
+        <v>1.74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4362,6 +4362,32 @@
         <v>1.74</v>
       </c>
     </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B154">
+        <v>6.02</v>
+      </c>
+      <c r="C154">
+        <v>3.58</v>
+      </c>
+      <c r="D154">
+        <v>5.4</v>
+      </c>
+      <c r="E154">
+        <v>1.38</v>
+      </c>
+      <c r="F154">
+        <v>2.54</v>
+      </c>
+      <c r="G154">
+        <v>0.8</v>
+      </c>
+      <c r="H154">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4388,6 +4388,32 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B155">
+        <v>6.19</v>
+      </c>
+      <c r="C155">
+        <v>3.57</v>
+      </c>
+      <c r="D155">
+        <v>4.82</v>
+      </c>
+      <c r="E155">
+        <v>1.39</v>
+      </c>
+      <c r="F155">
+        <v>2.54</v>
+      </c>
+      <c r="G155">
+        <v>1.04</v>
+      </c>
+      <c r="H155">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4414,6 +4414,32 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B156">
+        <v>6.41</v>
+      </c>
+      <c r="C156">
+        <v>3.81</v>
+      </c>
+      <c r="D156">
+        <v>5.36</v>
+      </c>
+      <c r="E156">
+        <v>1.24</v>
+      </c>
+      <c r="F156">
+        <v>3.02</v>
+      </c>
+      <c r="G156">
+        <v>1.44</v>
+      </c>
+      <c r="H156">
+        <v>2.1800000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/메인뉴스2026.xlsx
+++ b/메인뉴스2026.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4440,6 +4440,32 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B157">
+        <v>6.95</v>
+      </c>
+      <c r="C157">
+        <v>3.99</v>
+      </c>
+      <c r="D157">
+        <v>6.01</v>
+      </c>
+      <c r="E157">
+        <v>1.45</v>
+      </c>
+      <c r="F157">
+        <v>2.91</v>
+      </c>
+      <c r="G157">
+        <v>1.25</v>
+      </c>
+      <c r="H157">
+        <v>1.81</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
